--- a/medical_surveys_questionnaires/015_public_health_information_credibility_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/015_public_health_information_credibility_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>newspaper</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newspaper</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
@@ -1216,80 +1216,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>health_info_source_choices</t>
+          <t>trust_level_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tv</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>Very low</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>health_info_source_choices</t>
+          <t>trust_level_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>health_info_source_choices</t>
+          <t>trust_level_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>health_info_source_choices</t>
+          <t>trust_level_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1301,80 +1301,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>very_low</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Very low</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trust_level_choices</t>
+          <t>credibility_source_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high_school_or_below</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High school or below</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trust_level_choices</t>
+          <t>credibility_source_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trust_level_choices</t>
+          <t>credibility_source_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Bachelor's degree</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trust_level_choices</t>
+          <t>credibility_source_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>postgraduate_degree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very high</t>
+          <t>Postgraduate degree</t>
         </is>
       </c>
     </row>
@@ -1386,78 +1386,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>high_school_or_below</t>
+          <t>doctoral_degree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>High school or below</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>credibility_source_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>some_college</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Some college</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>credibility_source_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>bachelor's_degree</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bachelor's degree</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>credibility_source_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>postgraduate_degree</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Postgraduate degree</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>credibility_source_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>doctoral_degree</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Doctoral degree</t>
         </is>
